--- a/data/Data_for_figures_4results/Result1.xlsx
+++ b/data/Data_for_figures_4results/Result1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\State_SDG\Github\SDG_Interactions-driven-by-Urban_Typologies\data\Data_for_figures_4results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\City SDG paper\data for governance capacity\WGI_data_072026\1_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F12AF89-F9DC-475E-BFCC-C6B117705D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94BAC53A-821B-4585-86F3-E41E9093A15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3456" yWindow="3456" windowWidth="15648" windowHeight="11316" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -375,10 +375,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -406,7 +412,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,2128 +696,2129 @@
   <dimension ref="A1:F106"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.5546875" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="16.109375" customWidth="1"/>
     <col min="5" max="5" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1">
-        <v>47.995117507811045</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C2">
+        <v>47.996798269466737</v>
+      </c>
+      <c r="D2">
         <v>301.73044430983902</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2">
         <v>46.035209415711336</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>0.4014687000614825</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="1">
-        <v>58.203232133680245</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3">
+        <v>58.207606377212748</v>
+      </c>
+      <c r="D3">
         <v>121.69335212716466</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3">
         <v>52.499018267004296</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>0.53999611346066856</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="1">
-        <v>50.211559979686754</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="C4">
+        <v>50.218342179386795</v>
+      </c>
+      <c r="D4">
         <v>37.977776089596567</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4">
         <v>42.188644778904695</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4">
         <v>0.35683089857472589</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="1">
-        <v>46.867240984465312</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5">
+        <v>46.879618164040963</v>
+      </c>
+      <c r="D5">
         <v>223.39370727468443</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5">
         <v>45.937778835286423</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5">
         <v>0.44341842589078428</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="1">
-        <v>48.207330061515222</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6">
+        <v>48.217147668969019</v>
+      </c>
+      <c r="D6">
         <v>261.54220994857474</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6">
         <v>56.862021776640688</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
         <v>0.41567702771782827</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="1">
-        <v>35.349451326961571</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="C7">
+        <v>35.362798703833455</v>
+      </c>
+      <c r="D7">
         <v>66.621012689490641</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7">
         <v>34.81684981684981</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>0.2987401698992081</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1">
-        <v>61.658101424952243</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C8">
+        <v>61.660947192123629</v>
+      </c>
+      <c r="D8">
         <v>193.50848353907372</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8">
         <v>63.838867733515073</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>0.45400724678207838</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="1">
-        <v>36.740632858044826</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C9">
+        <v>36.755091363893001</v>
+      </c>
+      <c r="D9">
         <v>42.40348978065451</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9">
         <v>37.614248493201913</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9">
         <v>0.51217434689558783</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1">
-        <v>49.561096013364569</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10">
+        <v>49.57060881056826</v>
+      </c>
+      <c r="D10">
         <v>416.78358494982871</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10">
         <v>59.078583065514074</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>0.32511717269327339</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="1">
-        <v>31.717980218351226</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11">
+        <v>31.717945339058584</v>
+      </c>
+      <c r="D11">
         <v>79.979912982805047</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11">
         <v>53.964531941752107</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>0.26364522850364691</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="1">
-        <v>37.03910221767633</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C12">
+        <v>37.031532026140788</v>
+      </c>
+      <c r="D12">
         <v>84.086649009126361</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12">
         <v>48.64033703047555</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12">
         <v>0.35613430126010792</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="1">
-        <v>50.943311440022072</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C13">
+        <v>50.955515202341651</v>
+      </c>
+      <c r="D13">
         <v>23.307983932533126</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13">
         <v>41.424816597519715</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13">
         <v>0.4360287164738767</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="1">
-        <v>63.865698399078227</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="C14">
+        <v>63.865059594124389</v>
+      </c>
+      <c r="D14">
         <v>535.70554312326567</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14">
         <v>78.465123039633156</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14">
         <v>0.51138589482240004</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="1">
-        <v>54.249365551721681</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="C15">
+        <v>54.244762008982711</v>
+      </c>
+      <c r="D15">
         <v>586.85480488345297</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15">
         <v>87.081978396098194</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15">
         <v>0.53828907059811071</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="1">
-        <v>46.510071762735798</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="C16">
+        <v>46.511602462505309</v>
+      </c>
+      <c r="D16">
         <v>280.46434242129521</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16">
         <v>44.842970437768727</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16">
         <v>0.53490048271621449</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="1">
-        <v>49.152171368687149</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="C17">
+        <v>49.152466806820669</v>
+      </c>
+      <c r="D17">
         <v>364.02352450271644</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17">
         <v>32.783026525112824</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17">
         <v>0.56590278828268759</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="1">
-        <v>44.334304137209259</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="C18">
+        <v>44.343607784118852</v>
+      </c>
+      <c r="D18">
         <v>115.68290662066357</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18">
         <v>46.497239733911123</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18">
         <v>0.39003985761735988</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="1">
-        <v>47.984610253224346</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="C19">
+        <v>47.987647374758588</v>
+      </c>
+      <c r="D19">
         <v>192.52776431536765</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19">
         <v>58.064273424398237</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19">
         <v>0.49547090348422951</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="1">
-        <v>39.707081194598764</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="C20">
+        <v>39.698864136870192</v>
+      </c>
+      <c r="D20">
         <v>102.55913563057872</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20">
         <v>42.216639393305897</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>0.37577804272271748</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="1">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="1">
-        <v>52.749197132440621</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="C21">
+        <v>52.746349645601363</v>
+      </c>
+      <c r="D21">
         <v>511.53607531888616</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21">
         <v>61.164613203732578</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>0.45874056852788297</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="1">
+      <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="1">
-        <v>45.291661413615401</v>
-      </c>
-      <c r="D22" s="1">
+      <c r="C22">
+        <v>45.291317446417573</v>
+      </c>
+      <c r="D22">
         <v>202.12372022902713</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22">
         <v>54.670741113362126</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22">
         <v>0.40282463478376129</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="1">
+      <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="1">
-        <v>45.160070388637997</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="C23">
+        <v>45.161640556320584</v>
+      </c>
+      <c r="D23">
         <v>397.61972729552622</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23">
         <v>58.469704358368098</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23">
         <v>0.43078195934296359</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+      <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="1">
-        <v>45.187844521824466</v>
-      </c>
-      <c r="D24" s="1">
+      <c r="C24">
+        <v>45.202455879237753</v>
+      </c>
+      <c r="D24">
         <v>104.13657756636698</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24">
         <v>39.904514296607992</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>0.52012518189743928</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="1">
-        <v>38.048526659785331</v>
-      </c>
-      <c r="D25" s="1">
+      <c r="C25">
+        <v>38.056277569701209</v>
+      </c>
+      <c r="D25">
         <v>86.021710522413684</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25">
         <v>42.934337288061634</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>0.39440867940913249</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="1">
+      <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="1">
-        <v>47.022322891028431</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="C26">
+        <v>47.026030475685282</v>
+      </c>
+      <c r="D26">
         <v>167.32749810734546</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26">
         <v>56.404767345367951</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26">
         <v>0.47093804045818172</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="1">
+      <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="1">
-        <v>46.337510964602728</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="C27">
+        <v>46.346022442271568</v>
+      </c>
+      <c r="D27">
         <v>307.93238629105321</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27">
         <v>64.817155754377524</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27">
         <v>0.38575571342524723</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="1">
+      <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="1">
-        <v>41.536772083014085</v>
-      </c>
-      <c r="D28" s="1">
+      <c r="C28">
+        <v>41.540209945751357</v>
+      </c>
+      <c r="D28">
         <v>241.95485034602703</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28">
         <v>44.058121819829331</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28">
         <v>0.44068185836619639</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="1">
+      <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="1">
-        <v>37.623182309792853</v>
-      </c>
-      <c r="D29" s="1">
+      <c r="C29">
+        <v>37.630264384238444</v>
+      </c>
+      <c r="D29">
         <v>157.97783769567127</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29">
         <v>22.932769769655671</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29">
         <v>0.50678743203323051</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="1">
+      <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="1">
-        <v>55.151187494733634</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="C30">
+        <v>55.16063340257854</v>
+      </c>
+      <c r="D30">
         <v>133.61850756250357</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30">
         <v>64.379288747041002</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30">
         <v>0.57233182098357227</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+      <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="1">
-        <v>55.615032172120699</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="C31">
+        <v>55.635140133254168</v>
+      </c>
+      <c r="D31">
         <v>86.525260862038593</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31">
         <v>75.909838971623032</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>0.51707073111260105</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="1">
-        <v>47.045175013169008</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="C32">
+        <v>47.053775026595559</v>
+      </c>
+      <c r="D32">
         <v>428.17212083441473</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32">
         <v>52.879409747549388</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32">
         <v>0.40426633870232548</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="1">
+      <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="1">
-        <v>50.613853081905738</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="C33">
+        <v>50.604316481191105</v>
+      </c>
+      <c r="D33">
         <v>124.64057624892394</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33">
         <v>65.696440781914177</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33">
         <v>0.50010828016245501</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1">
+      <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="1">
-        <v>42.137853006272636</v>
-      </c>
-      <c r="D34" s="1">
+      <c r="C34">
+        <v>42.136793321817542</v>
+      </c>
+      <c r="D34">
         <v>58.269365329681726</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34">
         <v>30.061340228818398</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34">
         <v>0.36137101438818192</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="1">
+      <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="1">
-        <v>43.25203389504837</v>
-      </c>
-      <c r="D35" s="1">
+      <c r="C35">
+        <v>43.264398867658556</v>
+      </c>
+      <c r="D35">
         <v>64.106584295320914</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35">
         <v>36.255566057285534</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35">
         <v>0.48145044562830391</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="1">
+      <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="1">
-        <v>52.682097166550754</v>
-      </c>
-      <c r="D36" s="1">
+      <c r="C36">
+        <v>52.687858644088926</v>
+      </c>
+      <c r="D36">
         <v>153.17908683089928</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36">
         <v>49.790721103413894</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36">
         <v>0.39876381414723427</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="1">
+      <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="1">
-        <v>46.208984144863422</v>
-      </c>
-      <c r="D37" s="1">
+      <c r="C37">
+        <v>46.209021181906827</v>
+      </c>
+      <c r="D37">
         <v>147.41074089261687</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37">
         <v>46.763988733341741</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37">
         <v>0.38278942441928948</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+      <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C38" s="1">
-        <v>43.575303917751697</v>
-      </c>
-      <c r="D38" s="1">
+      <c r="C38">
+        <v>43.570878884161928</v>
+      </c>
+      <c r="D38">
         <v>127.60555293330985</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38">
         <v>40.77024476433801</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38">
         <v>0.40541968327839001</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C39" s="1">
-        <v>45.050778789980626</v>
-      </c>
-      <c r="D39" s="1">
+      <c r="C39">
+        <v>45.053625620899616</v>
+      </c>
+      <c r="D39">
         <v>136.13588030896972</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39">
         <v>56.812081769111195</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39">
         <v>0.44655411477026741</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="1">
+      <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C40" s="1">
-        <v>46.579877209524405</v>
-      </c>
-      <c r="D40" s="1">
+      <c r="C40">
+        <v>46.577842651066767</v>
+      </c>
+      <c r="D40">
         <v>308.48107821367387</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40">
         <v>65.476893788850163</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40">
         <v>0.50503876609349996</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+      <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="1">
-        <v>41.564450370332224</v>
-      </c>
-      <c r="D41" s="1">
+      <c r="C41">
+        <v>41.56505673310555</v>
+      </c>
+      <c r="D41">
         <v>321.95245671182778</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41">
         <v>63.311370581073987</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41">
         <v>0.35806094713200959</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="1">
+      <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C42" s="1">
-        <v>41.351007130274517</v>
-      </c>
-      <c r="D42" s="1">
+      <c r="C42">
+        <v>41.353800756218057</v>
+      </c>
+      <c r="D42">
         <v>181.73869340260842</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42">
         <v>60.485659272867736</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42">
         <v>0.3909957685745053</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="1">
+      <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="1">
-        <v>31.711215568310433</v>
-      </c>
-      <c r="D43" s="1">
+      <c r="C43">
+        <v>31.701756452115607</v>
+      </c>
+      <c r="D43">
         <v>48.080106358624022</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43">
         <v>45.384022640179403</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43">
         <v>0.29566869553494041</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="1">
+      <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="1">
-        <v>44.818066229916305</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="C44">
+        <v>44.829172138461459</v>
+      </c>
+      <c r="D44">
         <v>181.46054329304025</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44">
         <v>43.741445069037461</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44">
         <v>0.46724569277492728</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="1">
+      <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C45" s="1">
-        <v>47.83802609496469</v>
-      </c>
-      <c r="D45" s="1">
+      <c r="C45">
+        <v>47.837354200184656</v>
+      </c>
+      <c r="D45">
         <v>113.17104093295553</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45">
         <v>53.794526891856634</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45">
         <v>0.38353859302216958</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="1">
+      <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="1">
-        <v>37.687511551926036</v>
-      </c>
-      <c r="D46" s="1">
+      <c r="C46">
+        <v>37.683929779103849</v>
+      </c>
+      <c r="D46">
         <v>96.820281017013784</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46">
         <v>41.21206460152596</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46">
         <v>0.31633909673932531</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="1">
+      <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C47" s="1">
-        <v>35.704490444545662</v>
-      </c>
-      <c r="D47" s="1">
+      <c r="C47">
+        <v>35.708225994523794</v>
+      </c>
+      <c r="D47">
         <v>147.51719648824565</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47">
         <v>26.653245601129235</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47">
         <v>0.43313097417475488</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="1">
+      <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C48" s="1">
-        <v>48.446422507829858</v>
-      </c>
-      <c r="D48" s="1">
+      <c r="C48">
+        <v>48.460867386302382</v>
+      </c>
+      <c r="D48">
         <v>222.08247479848262</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48">
         <v>46.361873115455246</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48">
         <v>0.39274742258605022</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C49" s="1">
-        <v>48.595738616261578</v>
-      </c>
-      <c r="D49" s="1">
+      <c r="C49">
+        <v>48.603615360767691</v>
+      </c>
+      <c r="D49">
         <v>107.83544447938507</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49">
         <v>43.583737243538003</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49">
         <v>0.49816901984103712</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C50" s="1">
-        <v>40.321208662814918</v>
-      </c>
-      <c r="D50" s="1">
+      <c r="C50">
+        <v>40.315897953010221</v>
+      </c>
+      <c r="D50">
         <v>69.766711108209662</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50">
         <v>46.391864318598749</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50">
         <v>0.30523284292479258</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+      <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C51" s="1">
-        <v>55.496913120328308</v>
-      </c>
-      <c r="D51" s="1">
+      <c r="C51">
+        <v>55.502082702878475</v>
+      </c>
+      <c r="D51">
         <v>1063.295423511343</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51">
         <v>67.76286520491719</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51">
         <v>0.54645768323906485</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C52" s="1">
-        <v>42.32549380065258</v>
-      </c>
-      <c r="D52" s="1">
+      <c r="C52">
+        <v>42.323687501050891</v>
+      </c>
+      <c r="D52">
         <v>139.58429860437417</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52">
         <v>50.783707782661189</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52">
         <v>0.35066175654546372</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+      <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="1">
-        <v>65.883247645489533</v>
-      </c>
-      <c r="D53" s="1">
+      <c r="C53">
+        <v>65.895683948241583</v>
+      </c>
+      <c r="D53">
         <v>76.343353779340944</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53">
         <v>66.638643901991657</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53">
         <v>0.50488626938420078</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C54" s="1">
-        <v>52.851644163444327</v>
-      </c>
-      <c r="D54" s="1">
+      <c r="C54">
+        <v>52.865397589936492</v>
+      </c>
+      <c r="D54">
         <v>180.49249071133224</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54">
         <v>61.272110852654521</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54">
         <v>0.48896719248065618</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="1">
+      <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C55" s="1">
-        <v>35.859421454394486</v>
-      </c>
-      <c r="D55" s="1">
+      <c r="C55">
+        <v>35.868246078907852</v>
+      </c>
+      <c r="D55">
         <v>211.53684122056438</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55">
         <v>20.509817454258993</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55">
         <v>0.36552599430043309</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="1">
+      <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C56" s="1">
-        <v>34.601406669998958</v>
-      </c>
-      <c r="D56" s="1">
+      <c r="C56">
+        <v>34.599663152548715</v>
+      </c>
+      <c r="D56">
         <v>104.28669206880406</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56">
         <v>46.084807511513965</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56">
         <v>0.31508540673480689</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
+      <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="1">
-        <v>46.436091529006262</v>
-      </c>
-      <c r="D57" s="1">
+      <c r="C57">
+        <v>46.4405497079226</v>
+      </c>
+      <c r="D57">
         <v>469.05540278241511</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57">
         <v>48.140034526071858</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57">
         <v>0.50670051371530367</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C58" s="1">
-        <v>45.696154297035925</v>
-      </c>
-      <c r="D58" s="1">
+      <c r="C58">
+        <v>45.691396939879375</v>
+      </c>
+      <c r="D58">
         <v>418.32648645623652</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58">
         <v>58.342786232518478</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58">
         <v>0.47554818745075528</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+      <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="1">
-        <v>59.357310410137451</v>
-      </c>
-      <c r="D59" s="1">
+      <c r="C59">
+        <v>59.367653966035057</v>
+      </c>
+      <c r="D59">
         <v>182.03842719315199</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59">
         <v>62.809217750952762</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59">
         <v>0.56223834564200581</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+      <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C60" s="1">
-        <v>45.998914704833929</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="C60">
+        <v>46.019459727761586</v>
+      </c>
+      <c r="D60">
         <v>141.40662129952005</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60">
         <v>32.768813230175638</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60">
         <v>0.51899498772394836</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+      <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C61" s="1">
-        <v>48.101485720993765</v>
-      </c>
-      <c r="D61" s="1">
+      <c r="C61">
+        <v>48.105613259294465</v>
+      </c>
+      <c r="D61">
         <v>116.66711772496114</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61">
         <v>60.767997075977327</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61">
         <v>0.36441612640465532</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
+      <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="1">
-        <v>49.388405089717509</v>
-      </c>
-      <c r="D62" s="1">
+      <c r="C62">
+        <v>49.392605509304786</v>
+      </c>
+      <c r="D62">
         <v>549.56915735073699</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62">
         <v>45.839604386153518</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62">
         <v>0.49208619905417889</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="1">
+      <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C63" s="1">
-        <v>38.357876424999567</v>
-      </c>
-      <c r="D63" s="1">
+      <c r="C63">
+        <v>38.356363350187188</v>
+      </c>
+      <c r="D63">
         <v>153.82871796474419</v>
       </c>
-      <c r="E63" s="1">
+      <c r="E63">
         <v>52.535661040225371</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63">
         <v>0.31524141617293971</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
+      <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C64" s="1">
-        <v>58.082767477461623</v>
-      </c>
-      <c r="D64" s="1">
+      <c r="C64">
+        <v>58.070926782067005</v>
+      </c>
+      <c r="D64">
         <v>946.09623825009419</v>
       </c>
-      <c r="E64" s="1">
+      <c r="E64">
         <v>71.083746586515275</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64">
         <v>0.56045530388045883</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="1">
+      <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C65" s="1">
-        <v>48.151833727149459</v>
-      </c>
-      <c r="D65" s="1">
+      <c r="C65">
+        <v>48.154207567533518</v>
+      </c>
+      <c r="D65">
         <v>239.18584587234989</v>
       </c>
-      <c r="E65" s="1">
+      <c r="E65">
         <v>33.571934533795627</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65">
         <v>0.52878260243351427</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="1">
+      <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C66" s="1">
-        <v>45.516236561179198</v>
-      </c>
-      <c r="D66" s="1">
+      <c r="C66">
+        <v>45.50918715193334</v>
+      </c>
+      <c r="D66">
         <v>35.595218677942448</v>
       </c>
-      <c r="E66" s="1">
+      <c r="E66">
         <v>33.495012354717673</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66">
         <v>0.40639239112963987</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="1">
+      <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C67" s="1">
-        <v>39.509704078209595</v>
-      </c>
-      <c r="D67" s="1">
+      <c r="C67">
+        <v>39.515625080633704</v>
+      </c>
+      <c r="D67">
         <v>96.934016688459309</v>
       </c>
-      <c r="E67" s="1">
+      <c r="E67">
         <v>48.935599756312072</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67">
         <v>0.29258421068882112</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="1">
+      <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C68" s="1">
-        <v>50.384998850340622</v>
-      </c>
-      <c r="D68" s="1">
+      <c r="C68">
+        <v>50.391494793817387</v>
+      </c>
+      <c r="D68">
         <v>82.920937762296148</v>
       </c>
-      <c r="E68" s="1">
+      <c r="E68">
         <v>60.190497803430588</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68">
         <v>0.45893564945810178</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="1">
+      <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="1">
-        <v>45.175305952010966</v>
-      </c>
-      <c r="D69" s="1">
+      <c r="C69">
+        <v>45.185047014515092</v>
+      </c>
+      <c r="D69">
         <v>278.36094335637557</v>
       </c>
-      <c r="E69" s="1">
+      <c r="E69">
         <v>45.807466717878619</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69">
         <v>0.45622209843508332</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="1">
+      <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="1">
-        <v>55.740722654719164</v>
-      </c>
-      <c r="D70" s="1">
+      <c r="C70">
+        <v>55.737245924256293</v>
+      </c>
+      <c r="D70">
         <v>178.95847934862843</v>
       </c>
-      <c r="E70" s="1">
+      <c r="E70">
         <v>50.806405353168905</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70">
         <v>0.55318650586410456</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="1">
+      <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C71" s="1">
-        <v>44.540640868471513</v>
-      </c>
-      <c r="D71" s="1">
+      <c r="C71">
+        <v>44.548606060762062</v>
+      </c>
+      <c r="D71">
         <v>224.07272243121065</v>
       </c>
-      <c r="E71" s="1">
+      <c r="E71">
         <v>33.063911114430326</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71">
         <v>0.44733405212221761</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="1">
+      <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C72" s="1">
-        <v>49.017063183411331</v>
-      </c>
-      <c r="D72" s="1">
+      <c r="C72">
+        <v>49.01886938167911</v>
+      </c>
+      <c r="D72">
         <v>511.39565281454998</v>
       </c>
-      <c r="E72" s="1">
+      <c r="E72">
         <v>63.51859871524838</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72">
         <v>0.46541324210160467</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="1">
+      <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="1">
-        <v>49.559695228273206</v>
-      </c>
-      <c r="D73" s="1">
+      <c r="C73">
+        <v>49.571103830788296</v>
+      </c>
+      <c r="D73">
         <v>125.57926200792653</v>
       </c>
-      <c r="E73" s="1">
+      <c r="E73">
         <v>44.53366601439226</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73">
         <v>0.41736069758194222</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="1">
+      <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="C74" s="1">
-        <v>49.79697939015378</v>
-      </c>
-      <c r="D74" s="1">
+      <c r="C74">
+        <v>49.80503141310146</v>
+      </c>
+      <c r="D74">
         <v>170.58160025598809</v>
       </c>
-      <c r="E74" s="1">
+      <c r="E74">
         <v>56.23718857770767</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74">
         <v>0.45040192900531889</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="1">
+      <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C75" s="1">
-        <v>66.332773675454092</v>
-      </c>
-      <c r="D75" s="1">
+      <c r="C75">
+        <v>66.348286780529094</v>
+      </c>
+      <c r="D75">
         <v>141.55774388752863</v>
       </c>
-      <c r="E75" s="1">
+      <c r="E75">
         <v>63.858522736543257</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75">
         <v>0.6289143514774912</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="1">
+      <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C76" s="1">
-        <v>53.791282950909199</v>
-      </c>
-      <c r="D76" s="1">
+      <c r="C76">
+        <v>53.791486261186414</v>
+      </c>
+      <c r="D76">
         <v>394.38955710620945</v>
       </c>
-      <c r="E76" s="1">
+      <c r="E76">
         <v>44.252684252018042</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76">
         <v>0.47346738091719148</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="1">
+      <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C77" s="1">
-        <v>49.722507262501253</v>
-      </c>
-      <c r="D77" s="1">
+      <c r="C77">
+        <v>49.710687116791824</v>
+      </c>
+      <c r="D77">
         <v>44.202962934557071</v>
       </c>
-      <c r="E77" s="1">
+      <c r="E77">
         <v>35.913534236284924</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77">
         <v>0.47523249689229208</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="1">
+      <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C78" s="1">
-        <v>59.287955202819035</v>
-      </c>
-      <c r="D78" s="1">
+      <c r="C78">
+        <v>59.292052924270607</v>
+      </c>
+      <c r="D78">
         <v>243.4026715961638</v>
       </c>
-      <c r="E78" s="1">
+      <c r="E78">
         <v>54.398279053149665</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78">
         <v>0.51205507980505105</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="1">
+      <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="1">
-        <v>44.075578836052337</v>
-      </c>
-      <c r="D79" s="1">
+      <c r="C79">
+        <v>44.076733120725137</v>
+      </c>
+      <c r="D79">
         <v>109.83751789582472</v>
       </c>
-      <c r="E79" s="1">
+      <c r="E79">
         <v>54.302595387003095</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79">
         <v>0.4038606307602981</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="1">
+      <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C80" s="1">
-        <v>45.800795675077055</v>
-      </c>
-      <c r="D80" s="1">
+      <c r="C80">
+        <v>45.821873581087814</v>
+      </c>
+      <c r="D80">
         <v>64.87037314453876</v>
       </c>
-      <c r="E80" s="1">
+      <c r="E80">
         <v>29.686923528654102</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80">
         <v>0.59295852510739833</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="1">
+      <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C81" s="1">
-        <v>49.10995257938054</v>
-      </c>
-      <c r="D81" s="1">
+      <c r="C81">
+        <v>49.111324463160052</v>
+      </c>
+      <c r="D81">
         <v>127.42337434095155</v>
       </c>
-      <c r="E81" s="1">
+      <c r="E81">
         <v>44.996604659965044</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81">
         <v>0.53177638273948247</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="1">
+      <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C82" s="1">
-        <v>54.179958526502269</v>
-      </c>
-      <c r="D82" s="1">
+      <c r="C82">
+        <v>54.19669685423046</v>
+      </c>
+      <c r="D82">
         <v>176.19657301409379</v>
       </c>
-      <c r="E82" s="1">
+      <c r="E82">
         <v>46.768785023252775</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82">
         <v>0.56459205908268162</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="1">
+      <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C83" s="1">
-        <v>51.886983906951691</v>
-      </c>
-      <c r="D83" s="1">
+      <c r="C83">
+        <v>51.897061669347622</v>
+      </c>
+      <c r="D83">
         <v>60.45300005587962</v>
       </c>
-      <c r="E83" s="1">
+      <c r="E83">
         <v>61.809235270404493</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83">
         <v>0.4363084731388322</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="1">
+      <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C84" s="1">
-        <v>46.851065037147698</v>
-      </c>
-      <c r="D84" s="1">
+      <c r="C84">
+        <v>46.858673394599833</v>
+      </c>
+      <c r="D84">
         <v>130.6222757838832</v>
       </c>
-      <c r="E84" s="1">
+      <c r="E84">
         <v>47.793954180601737</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84">
         <v>0.3761358659816223</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="1">
+      <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C85" s="1">
-        <v>63.297924984189031</v>
-      </c>
-      <c r="D85" s="1">
+      <c r="C85">
+        <v>63.306115169554033</v>
+      </c>
+      <c r="D85">
         <v>306.24369828411545</v>
       </c>
-      <c r="E85" s="1">
+      <c r="E85">
         <v>60.516795323704905</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85">
         <v>0.54213485010399787</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="1">
+      <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C86" s="1">
-        <v>69.770061374920772</v>
-      </c>
-      <c r="D86" s="1">
+      <c r="C86">
+        <v>69.789165876778071</v>
+      </c>
+      <c r="D86">
         <v>738.86348799087727</v>
       </c>
-      <c r="E86" s="1">
+      <c r="E86">
         <v>89.977972892675552</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86">
         <v>0.63371057167621292</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="1">
+      <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C87" s="1">
-        <v>66.755681533212041</v>
-      </c>
-      <c r="D87" s="1">
+      <c r="C87">
+        <v>66.761452126061087</v>
+      </c>
+      <c r="D87">
         <v>287.92982728617204</v>
       </c>
-      <c r="E87" s="1">
+      <c r="E87">
         <v>128.30810477852228</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87">
         <v>0.5609933928581351</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="1">
+      <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C88" s="1">
-        <v>42.633408749923298</v>
-      </c>
-      <c r="D88" s="1">
+      <c r="C88">
+        <v>42.654746522757961</v>
+      </c>
+      <c r="D88">
         <v>122.79463485141791</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88">
         <v>37.416325487103592</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88">
         <v>0.40875762591464387</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="1">
+      <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C89" s="1">
-        <v>66.804038066226994</v>
-      </c>
-      <c r="D89" s="1">
+      <c r="C89">
+        <v>66.825181093319557</v>
+      </c>
+      <c r="D89">
         <v>254.36246635827453</v>
       </c>
-      <c r="E89" s="1">
+      <c r="E89">
         <v>80.833535468675564</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89">
         <v>0.58427084846222554</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="1">
+      <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C90" s="1">
-        <v>48.996310067696392</v>
-      </c>
-      <c r="D90" s="1">
+      <c r="C90">
+        <v>49.003755860671475</v>
+      </c>
+      <c r="D90">
         <v>38.619635712334706</v>
       </c>
-      <c r="E90" s="1">
+      <c r="E90">
         <v>38.98520444238877</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90">
         <v>0.53202455236395285</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="1">
+      <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C91" s="1">
-        <v>48.354668115134047</v>
-      </c>
-      <c r="D91" s="1">
+      <c r="C91">
+        <v>48.354920017761486</v>
+      </c>
+      <c r="D91">
         <v>213.13292069664081</v>
       </c>
-      <c r="E91" s="1">
+      <c r="E91">
         <v>38.07476268578268</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91">
         <v>0.46974431800549987</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="1">
+      <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C92" s="1">
-        <v>43.236555848015534</v>
-      </c>
-      <c r="D92" s="1">
+      <c r="C92">
+        <v>43.234940166210798</v>
+      </c>
+      <c r="D92">
         <v>137.83680872030578</v>
       </c>
-      <c r="E92" s="1">
+      <c r="E92">
         <v>49.696567702663422</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92">
         <v>0.44199759596035898</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="1">
+      <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C93" s="1">
-        <v>47.682084670428928</v>
-      </c>
-      <c r="D93" s="1">
+      <c r="C93">
+        <v>47.693831808158428</v>
+      </c>
+      <c r="D93">
         <v>206.7067628992821</v>
       </c>
-      <c r="E93" s="1">
+      <c r="E93">
         <v>31.600807057459914</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93">
         <v>0.50288272436204207</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="1">
+      <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C94" s="1">
-        <v>47.226935668786027</v>
-      </c>
-      <c r="D94" s="1">
+      <c r="C94">
+        <v>47.228600184442051</v>
+      </c>
+      <c r="D94">
         <v>106.01536440168086</v>
       </c>
-      <c r="E94" s="1">
+      <c r="E94">
         <v>44.642898047006831</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94">
         <v>0.50349050302966214</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="1">
+      <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C95" s="1">
-        <v>46.658952894246745</v>
-      </c>
-      <c r="D95" s="1">
+      <c r="C95">
+        <v>46.666319687757699</v>
+      </c>
+      <c r="D95">
         <v>474.65495958076491</v>
       </c>
-      <c r="E95" s="1">
+      <c r="E95">
         <v>41.221466397575988</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95">
         <v>0.45837042242575943</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="1">
+      <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C96" s="1">
-        <v>39.63342336376887</v>
-      </c>
-      <c r="D96" s="1">
+      <c r="C96">
+        <v>39.632137459974928</v>
+      </c>
+      <c r="D96">
         <v>170.92696766030897</v>
       </c>
-      <c r="E96" s="1">
+      <c r="E96">
         <v>46.88007315279259</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96">
         <v>0.42856717751583162</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="1">
+      <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C97" s="1">
-        <v>54.116738145111803</v>
-      </c>
-      <c r="D97" s="1">
+      <c r="C97">
+        <v>54.103517394824806</v>
+      </c>
+      <c r="D97">
         <v>644.88331383919103</v>
       </c>
-      <c r="E97" s="1">
+      <c r="E97">
         <v>68.739609268465813</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97">
         <v>0.54217663322045406</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="1">
+      <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C98" s="1">
-        <v>47.666231610341818</v>
-      </c>
-      <c r="D98" s="1">
+      <c r="C98">
+        <v>47.689239753155746</v>
+      </c>
+      <c r="D98">
         <v>42.982898726384647</v>
       </c>
-      <c r="E98" s="1">
+      <c r="E98">
         <v>33.087627802563432</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98">
         <v>0.36402682127298969</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="1">
+      <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C99" s="1">
-        <v>39.619693959900857</v>
-      </c>
-      <c r="D99" s="1">
+      <c r="C99">
+        <v>39.620074830126008</v>
+      </c>
+      <c r="D99">
         <v>61.013963086401397</v>
       </c>
-      <c r="E99" s="1">
+      <c r="E99">
         <v>55.432475450986253</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99">
         <v>0.26071457489448518</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="1">
+      <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C100" s="1">
-        <v>58.228220956543943</v>
-      </c>
-      <c r="D100" s="1">
+      <c r="C100">
+        <v>58.24553729101369</v>
+      </c>
+      <c r="D100">
         <v>635.55028826482112</v>
       </c>
-      <c r="E100" s="1">
+      <c r="E100">
         <v>58.525261720527993</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F100">
         <v>0.37623490390398118</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="1">
+      <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C101" s="1">
-        <v>50.572088850504151</v>
-      </c>
-      <c r="D101" s="1">
+      <c r="C101">
+        <v>50.570620429863219</v>
+      </c>
+      <c r="D101">
         <v>248.1669717920295</v>
       </c>
-      <c r="E101" s="1">
+      <c r="E101">
         <v>47.449297953824775</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F101">
         <v>0.37690638827644668</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="1">
+      <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C102" s="1">
-        <v>67.389684120323821</v>
-      </c>
-      <c r="D102" s="1">
+      <c r="C102">
+        <v>67.394744512354109</v>
+      </c>
+      <c r="D102">
         <v>384.22574662449045</v>
       </c>
-      <c r="E102" s="1">
+      <c r="E102">
         <v>73.998304569458753</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F102">
         <v>0.51269334834079372</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="1">
+      <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C103" s="1">
-        <v>40.244094317820263</v>
-      </c>
-      <c r="D103" s="1">
+      <c r="C103">
+        <v>40.248650961503117</v>
+      </c>
+      <c r="D103">
         <v>49.805623962157654</v>
       </c>
-      <c r="E103" s="1">
+      <c r="E103">
         <v>45.797488794231462</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F103">
         <v>0.35189357489292128</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="1">
+      <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="C104" s="1">
-        <v>38.286747968124224</v>
-      </c>
-      <c r="D104" s="1">
+      <c r="C104">
+        <v>38.281017336610098</v>
+      </c>
+      <c r="D104">
         <v>128.35522529322685</v>
       </c>
-      <c r="E104" s="1">
+      <c r="E104">
         <v>37.833984541725513</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F104">
         <v>0.37785896757983861</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="1">
+      <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C105" s="1">
-        <v>55.639117457440527</v>
-      </c>
-      <c r="D105" s="1">
+      <c r="C105">
+        <v>55.655036263196997</v>
+      </c>
+      <c r="D105">
         <v>179.83382655679264</v>
       </c>
-      <c r="E105" s="1">
+      <c r="E105">
         <v>40.528395978673174</v>
       </c>
-      <c r="F105" s="1">
+      <c r="F105">
         <v>0.48621380851523699</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="1">
+      <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C106" s="1">
-        <v>38.390205003183986</v>
-      </c>
-      <c r="D106" s="1">
+      <c r="C106">
+        <v>38.401700256850475</v>
+      </c>
+      <c r="D106">
         <v>122.92162069456097</v>
       </c>
-      <c r="E106" s="1">
+      <c r="E106">
         <v>31.84567634695512</v>
       </c>
-      <c r="F106" s="1">
+      <c r="F106">
         <v>0.38997244280538212</v>
       </c>
     </row>
